--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-familymemberhistory.xlsx
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -501,7 +501,7 @@
     <t>FamilyMemberHistory.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|ActivityDefinition|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -581,7 +581,7 @@
     <t>家族の歴史が利用できない理由を説明するコード。 / Codes describing the reason why a family member's history is not available.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/history-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/history-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -696,7 +696,7 @@
     <t>出生登録に文書化された出生時に割り当てられた性別を説明するコード。 / Codes describing the sex assigned at birth as documented on the birth registration.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>FamilyMemberHistory.born[x]</t>
@@ -801,7 +801,7 @@
     <t>家族の歴史が行われた理由を示すコード。 / Codes indicating why the family member history was done.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -915,7 +915,7 @@
     <t>状態または診断の識別。 / Identification of the Condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>.value</t>
@@ -933,7 +933,7 @@
     <t>患者の状態の結果。例えば死、永久障害、一時的な障害など。 / The result of the condition for the patient; e.g. death, permanent disability, temporary disability, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-outcome|4.0.1</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=OUTC)].target[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION].value</t>
@@ -1305,7 +1305,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.17578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
